--- a/AAII_Financials/Quarterly/BNNLF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNNLF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>BNNLF</t>
   </si>
@@ -656,121 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42369</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42277</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42185</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -781,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
@@ -790,7 +794,7 @@
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -816,8 +820,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -878,8 +885,11 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -940,8 +950,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -964,8 +977,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1026,8 +1040,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1088,20 +1105,23 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1111,11 +1131,11 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
@@ -1129,29 +1149,32 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-3000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-3100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1212,8 +1235,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1233,132 +1259,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="E17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>800</v>
       </c>
       <c r="K17" s="3">
         <v>800</v>
       </c>
       <c r="L17" s="3">
+        <v>800</v>
+      </c>
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>500</v>
       </c>
       <c r="V17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-500</v>
       </c>
       <c r="V18" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1381,20 +1414,21 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1426,11 +1460,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1443,70 +1477,76 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1100</v>
+        <v>-4000</v>
       </c>
       <c r="E21" s="3">
-        <v>-1900</v>
+        <v>-1200</v>
       </c>
       <c r="F21" s="3">
-        <v>-1300</v>
+        <v>-2000</v>
       </c>
       <c r="G21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>-700</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-900</v>
       </c>
       <c r="N21" s="3">
         <v>-900</v>
       </c>
       <c r="O21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-600</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-500</v>
       </c>
       <c r="V21" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1528,8 +1568,8 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1546,17 +1586,17 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>400</v>
       </c>
       <c r="T22" s="3">
         <v>400</v>
@@ -1567,70 +1607,76 @@
       <c r="V22" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1100</v>
+        <v>-4100</v>
       </c>
       <c r="E23" s="3">
-        <v>-1900</v>
+        <v>-1200</v>
       </c>
       <c r="F23" s="3">
-        <v>-1300</v>
+        <v>-2000</v>
       </c>
       <c r="G23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-700</v>
       </c>
       <c r="J23" s="3">
         <v>-700</v>
       </c>
       <c r="K23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-900</v>
       </c>
       <c r="N23" s="3">
         <v>-900</v>
       </c>
       <c r="O23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-900</v>
       </c>
       <c r="V23" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1674,25 +1720,28 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1753,90 +1802,96 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1100</v>
+        <v>-4100</v>
       </c>
       <c r="E26" s="3">
-        <v>-1900</v>
+        <v>-1200</v>
       </c>
       <c r="F26" s="3">
-        <v>-1300</v>
+        <v>-2000</v>
       </c>
       <c r="G26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-700</v>
       </c>
       <c r="J26" s="3">
         <v>-700</v>
       </c>
       <c r="K26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-900</v>
       </c>
       <c r="N26" s="3">
         <v>-900</v>
       </c>
       <c r="O26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-900</v>
       </c>
       <c r="V26" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1300</v>
-      </c>
       <c r="G27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-700</v>
       </c>
       <c r="J27" s="3">
         <v>-700</v>
@@ -1845,40 +1900,43 @@
         <v>-700</v>
       </c>
       <c r="L27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-900</v>
       </c>
       <c r="V27" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1939,8 +1997,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2001,8 +2062,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2063,8 +2127,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2125,20 +2192,23 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2170,11 +2240,11 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2187,28 +2257,31 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1300</v>
-      </c>
       <c r="G33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-700</v>
       </c>
       <c r="J33" s="3">
         <v>-700</v>
@@ -2217,40 +2290,43 @@
         <v>-700</v>
       </c>
       <c r="L33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-900</v>
       </c>
       <c r="V33" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2311,28 +2387,31 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1300</v>
-      </c>
       <c r="G35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-700</v>
       </c>
       <c r="J35" s="3">
         <v>-700</v>
@@ -2341,107 +2420,113 @@
         <v>-700</v>
       </c>
       <c r="L35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-900</v>
       </c>
       <c r="V35" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42369</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42277</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42185</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2464,8 +2549,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2488,106 +2574,110 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
-        <v>4500</v>
-      </c>
       <c r="G41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>26500</v>
+        <v>21200</v>
       </c>
       <c r="E42" s="3">
-        <v>29800</v>
+        <v>26900</v>
       </c>
       <c r="F42" s="3">
-        <v>29100</v>
+        <v>30300</v>
       </c>
       <c r="G42" s="3">
-        <v>5400</v>
+        <v>29600</v>
       </c>
       <c r="H42" s="3">
-        <v>7200</v>
+        <v>5500</v>
       </c>
       <c r="I42" s="3">
-        <v>1800</v>
+        <v>7300</v>
       </c>
       <c r="J42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K42" s="3">
         <v>2300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>4200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2597,8 +2687,8 @@
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2612,25 +2702,28 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -2642,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -2654,7 +2747,7 @@
         <v>100</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2663,19 +2756,22 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2736,8 +2832,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2745,13 +2844,13 @@
         <v>300</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>4800</v>
-      </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -2769,19 +2868,19 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
@@ -2790,89 +2889,95 @@
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>28100</v>
+        <v>23700</v>
       </c>
       <c r="E46" s="3">
-        <v>31100</v>
+        <v>28500</v>
       </c>
       <c r="F46" s="3">
-        <v>38400</v>
+        <v>31600</v>
       </c>
       <c r="G46" s="3">
-        <v>6000</v>
+        <v>39100</v>
       </c>
       <c r="H46" s="3">
-        <v>8100</v>
+        <v>6100</v>
       </c>
       <c r="I46" s="3">
-        <v>2000</v>
+        <v>8200</v>
       </c>
       <c r="J46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K46" s="3">
         <v>2800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6000</v>
+        <v>3100</v>
       </c>
       <c r="E47" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
+        <v>6100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>5900</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>4</v>
@@ -2883,20 +2988,20 @@
       <c r="I47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2907,8 +3012,8 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
@@ -2922,70 +3027,76 @@
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>39100</v>
+        <v>43900</v>
       </c>
       <c r="E48" s="3">
-        <v>38800</v>
+        <v>39700</v>
       </c>
       <c r="F48" s="3">
-        <v>39100</v>
+        <v>39500</v>
       </c>
       <c r="G48" s="3">
-        <v>36100</v>
+        <v>39800</v>
       </c>
       <c r="H48" s="3">
-        <v>35200</v>
+        <v>36700</v>
       </c>
       <c r="I48" s="3">
-        <v>33000</v>
+        <v>35800</v>
       </c>
       <c r="J48" s="3">
+        <v>33500</v>
+      </c>
+      <c r="K48" s="3">
         <v>31100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>41200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>40600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>39800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>33300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>33200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>43800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>45100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3046,8 +3157,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3108,8 +3222,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3170,13 +3287,16 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -3196,8 +3316,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3205,8 +3325,8 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -3217,8 +3337,8 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3232,8 +3352,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3294,70 +3417,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>73100</v>
+        <v>70800</v>
       </c>
       <c r="E54" s="3">
-        <v>75700</v>
+        <v>74300</v>
       </c>
       <c r="F54" s="3">
-        <v>77500</v>
+        <v>77000</v>
       </c>
       <c r="G54" s="3">
-        <v>42200</v>
+        <v>78900</v>
       </c>
       <c r="H54" s="3">
+        <v>42900</v>
+      </c>
+      <c r="I54" s="3">
+        <v>44100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>35600</v>
+      </c>
+      <c r="K54" s="3">
+        <v>33800</v>
+      </c>
+      <c r="L54" s="3">
+        <v>40900</v>
+      </c>
+      <c r="M54" s="3">
+        <v>42000</v>
+      </c>
+      <c r="N54" s="3">
+        <v>44000</v>
+      </c>
+      <c r="O54" s="3">
+        <v>45400</v>
+      </c>
+      <c r="P54" s="3">
+        <v>42800</v>
+      </c>
+      <c r="Q54" s="3">
         <v>43300</v>
       </c>
-      <c r="I54" s="3">
-        <v>35000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>33800</v>
-      </c>
-      <c r="K54" s="3">
-        <v>40900</v>
-      </c>
-      <c r="L54" s="3">
-        <v>42000</v>
-      </c>
-      <c r="M54" s="3">
-        <v>44000</v>
-      </c>
-      <c r="N54" s="3">
-        <v>45400</v>
-      </c>
-      <c r="O54" s="3">
-        <v>42800</v>
-      </c>
-      <c r="P54" s="3">
-        <v>43300</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>43200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>36300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>46900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>45600</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3380,8 +3509,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3404,31 +3534,32 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -3455,10 +3586,10 @@
         <v>100</v>
       </c>
       <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
         <v>800</v>
-      </c>
-      <c r="T57" s="3">
-        <v>500</v>
       </c>
       <c r="U57" s="3">
         <v>500</v>
@@ -3466,8 +3597,11 @@
       <c r="V57" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3492,8 +3626,8 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
@@ -3510,31 +3644,34 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3">
         <v>7700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>400</v>
@@ -3543,19 +3680,19 @@
         <v>400</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
       <c r="K59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
@@ -3590,25 +3727,28 @@
       <c r="V59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1300</v>
       </c>
-      <c r="E60" s="3">
-        <v>800</v>
-      </c>
       <c r="F60" s="3">
+        <v>900</v>
+      </c>
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>200</v>
       </c>
       <c r="I60" s="3">
         <v>200</v>
@@ -3617,13 +3757,13 @@
         <v>200</v>
       </c>
       <c r="K60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L60" s="3">
         <v>100</v>
       </c>
       <c r="M60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N60" s="3">
         <v>200</v>
@@ -3641,19 +3781,22 @@
         <v>200</v>
       </c>
       <c r="S60" s="3">
+        <v>200</v>
+      </c>
+      <c r="T60" s="3">
         <v>900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8300</v>
-      </c>
-      <c r="U60" s="3">
-        <v>600</v>
       </c>
       <c r="V60" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3709,13 +3852,16 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>7500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3747,7 +3893,7 @@
         <v>200</v>
       </c>
       <c r="M62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>300</v>
@@ -3762,10 +3908,10 @@
         <v>300</v>
       </c>
       <c r="R62" s="3">
+        <v>300</v>
+      </c>
+      <c r="S62" s="3">
         <v>200</v>
-      </c>
-      <c r="S62" s="3">
-        <v>300</v>
       </c>
       <c r="T62" s="3">
         <v>300</v>
@@ -3776,8 +3922,11 @@
       <c r="V62" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3838,8 +3987,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3900,8 +4052,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3962,25 +4117,28 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>400</v>
       </c>
       <c r="I66" s="3">
         <v>400</v>
@@ -3989,13 +4147,13 @@
         <v>400</v>
       </c>
       <c r="K66" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L66" s="3">
         <v>100</v>
       </c>
       <c r="M66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N66" s="3">
         <v>300</v>
@@ -4007,25 +4165,28 @@
         <v>300</v>
       </c>
       <c r="Q66" s="3">
+        <v>300</v>
+      </c>
+      <c r="R66" s="3">
         <v>600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4048,8 +4209,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4110,8 +4272,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4172,8 +4337,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4234,8 +4402,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4296,70 +4467,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-39600</v>
       </c>
-      <c r="E72" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-37600</v>
-      </c>
       <c r="G72" s="3">
-        <v>-36800</v>
+        <v>-38200</v>
       </c>
       <c r="H72" s="3">
-        <v>-36000</v>
+        <v>-37400</v>
       </c>
       <c r="I72" s="3">
-        <v>-35500</v>
+        <v>-36600</v>
       </c>
       <c r="J72" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="K72" s="3">
         <v>-35100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-34400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-34500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-55600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-52900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-55700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-53500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-53200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-56600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-49900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-47400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-46900</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4420,8 +4597,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4482,8 +4662,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4544,70 +4727,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>71900</v>
+        <v>70000</v>
       </c>
       <c r="E76" s="3">
-        <v>74800</v>
+        <v>73100</v>
       </c>
       <c r="F76" s="3">
-        <v>76300</v>
+        <v>76100</v>
       </c>
       <c r="G76" s="3">
-        <v>41600</v>
+        <v>77600</v>
       </c>
       <c r="H76" s="3">
-        <v>43000</v>
+        <v>42300</v>
       </c>
       <c r="I76" s="3">
-        <v>34500</v>
+        <v>43700</v>
       </c>
       <c r="J76" s="3">
+        <v>35100</v>
+      </c>
+      <c r="K76" s="3">
         <v>33400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>40800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>41900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>42500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>42600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>36900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>39300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4668,95 +4857,101 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42369</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42277</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42185</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42094</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1300</v>
-      </c>
       <c r="G81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-700</v>
       </c>
       <c r="J81" s="3">
         <v>-700</v>
@@ -4765,40 +4960,43 @@
         <v>-700</v>
       </c>
       <c r="L81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-900</v>
       </c>
       <c r="V81" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4821,8 +5019,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4883,8 +5082,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4945,8 +5147,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5007,8 +5212,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5069,8 +5277,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5131,8 +5342,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5193,70 +5407,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-700</v>
       </c>
       <c r="G89" s="3">
         <v>-700</v>
       </c>
       <c r="H89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-500</v>
       </c>
       <c r="K89" s="3">
         <v>-500</v>
       </c>
       <c r="L89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2100</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-400</v>
       </c>
       <c r="T89" s="3">
         <v>-400</v>
       </c>
       <c r="U89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5279,50 +5499,51 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -5333,16 +5554,19 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5403,8 +5627,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5465,37 +5692,40 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
-        <v>-6100</v>
-      </c>
       <c r="G94" s="3">
-        <v>-1900</v>
+        <v>-6200</v>
       </c>
       <c r="H94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-200</v>
       </c>
       <c r="K94" s="3">
         <v>-200</v>
       </c>
       <c r="L94" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="M94" s="3">
         <v>-300</v>
@@ -5504,31 +5734,34 @@
         <v>-300</v>
       </c>
       <c r="O94" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="P94" s="3">
         <v>-500</v>
       </c>
       <c r="Q94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5551,8 +5784,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5613,8 +5847,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5675,8 +5912,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5737,8 +5977,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5799,8 +6042,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5808,19 +6054,19 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>34500</v>
-      </c>
       <c r="G100" s="3">
-        <v>500</v>
+        <v>35100</v>
       </c>
       <c r="H100" s="3">
-        <v>7300</v>
+        <v>600</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5832,37 +6078,40 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>1400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5923,66 +6172,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3200</v>
+        <v>-4900</v>
       </c>
       <c r="E102" s="3">
-        <v>-2800</v>
+        <v>-3300</v>
       </c>
       <c r="F102" s="3">
-        <v>27600</v>
+        <v>-2900</v>
       </c>
       <c r="G102" s="3">
+        <v>28100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
-        <v>6100</v>
-      </c>
       <c r="I102" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-700</v>
       </c>
       <c r="M102" s="3">
         <v>-700</v>
       </c>
       <c r="N102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O102" s="3">
         <v>4500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BNNLF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNNLF_QTR_FIN.xlsx
@@ -1114,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1266,25 +1266,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="E17" s="3">
         <v>1600</v>
       </c>
       <c r="F17" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G17" s="3">
         <v>1400</v>
       </c>
       <c r="H17" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I17" s="3">
         <v>800</v>
       </c>
       <c r="J17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K17" s="3">
         <v>800</v>
@@ -1331,25 +1331,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="E18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-900</v>
       </c>
       <c r="I18" s="3">
         <v>-800</v>
       </c>
       <c r="J18" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="K18" s="3">
         <v>-800</v>
@@ -1486,7 +1486,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4000</v>
+        <v>-4100</v>
       </c>
       <c r="E21" s="3">
         <v>-1200</v>
@@ -1876,10 +1876,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="E27" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="F27" s="3">
         <v>-1900</v>
@@ -2266,10 +2266,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="E33" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="F33" s="3">
         <v>-1900</v>
@@ -2396,10 +2396,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="E35" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="F35" s="3">
         <v>-1900</v>
@@ -2581,7 +2581,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E41" s="3">
         <v>1100</v>
@@ -2590,7 +2590,7 @@
         <v>1000</v>
       </c>
       <c r="G41" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="H41" s="3">
         <v>500</v>
@@ -2646,22 +2646,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>21200</v>
+        <v>21500</v>
       </c>
       <c r="E42" s="3">
-        <v>26900</v>
+        <v>27300</v>
       </c>
       <c r="F42" s="3">
-        <v>30300</v>
+        <v>30700</v>
       </c>
       <c r="G42" s="3">
-        <v>29600</v>
+        <v>29900</v>
       </c>
       <c r="H42" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I42" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="J42" s="3">
         <v>1900</v>
@@ -2906,22 +2906,22 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>23700</v>
+        <v>24000</v>
       </c>
       <c r="E46" s="3">
-        <v>28500</v>
+        <v>28900</v>
       </c>
       <c r="F46" s="3">
-        <v>31600</v>
+        <v>32000</v>
       </c>
       <c r="G46" s="3">
-        <v>39100</v>
+        <v>39600</v>
       </c>
       <c r="H46" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="I46" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="J46" s="3">
         <v>2100</v>
@@ -2971,13 +2971,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="E47" s="3">
         <v>6100</v>
       </c>
       <c r="F47" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>4</v>
@@ -3036,25 +3036,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>43900</v>
+        <v>44500</v>
       </c>
       <c r="E48" s="3">
-        <v>39700</v>
+        <v>40200</v>
       </c>
       <c r="F48" s="3">
-        <v>39500</v>
+        <v>40000</v>
       </c>
       <c r="G48" s="3">
-        <v>39800</v>
+        <v>40300</v>
       </c>
       <c r="H48" s="3">
-        <v>36700</v>
+        <v>37200</v>
       </c>
       <c r="I48" s="3">
-        <v>35800</v>
+        <v>36300</v>
       </c>
       <c r="J48" s="3">
-        <v>33500</v>
+        <v>33900</v>
       </c>
       <c r="K48" s="3">
         <v>31100</v>
@@ -3426,25 +3426,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>70800</v>
+        <v>71700</v>
       </c>
       <c r="E54" s="3">
-        <v>74300</v>
+        <v>75300</v>
       </c>
       <c r="F54" s="3">
-        <v>77000</v>
+        <v>77900</v>
       </c>
       <c r="G54" s="3">
-        <v>78900</v>
+        <v>79900</v>
       </c>
       <c r="H54" s="3">
-        <v>42900</v>
+        <v>43400</v>
       </c>
       <c r="I54" s="3">
-        <v>44100</v>
+        <v>44600</v>
       </c>
       <c r="J54" s="3">
-        <v>35600</v>
+        <v>36000</v>
       </c>
       <c r="K54" s="3">
         <v>33800</v>
@@ -4135,7 +4135,7 @@
         <v>900</v>
       </c>
       <c r="G66" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="H66" s="3">
         <v>600</v>
@@ -4476,25 +4476,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-43600</v>
+        <v>-44100</v>
       </c>
       <c r="E72" s="3">
-        <v>-40200</v>
+        <v>-40800</v>
       </c>
       <c r="F72" s="3">
-        <v>-39600</v>
+        <v>-40100</v>
       </c>
       <c r="G72" s="3">
-        <v>-38200</v>
+        <v>-38700</v>
       </c>
       <c r="H72" s="3">
-        <v>-37400</v>
+        <v>-37900</v>
       </c>
       <c r="I72" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="J72" s="3">
         <v>-36600</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-36100</v>
       </c>
       <c r="K72" s="3">
         <v>-35100</v>
@@ -4736,25 +4736,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>70000</v>
+        <v>70900</v>
       </c>
       <c r="E76" s="3">
-        <v>73100</v>
+        <v>74000</v>
       </c>
       <c r="F76" s="3">
-        <v>76100</v>
+        <v>77000</v>
       </c>
       <c r="G76" s="3">
-        <v>77600</v>
+        <v>78600</v>
       </c>
       <c r="H76" s="3">
-        <v>42300</v>
+        <v>42800</v>
       </c>
       <c r="I76" s="3">
-        <v>43700</v>
+        <v>44200</v>
       </c>
       <c r="J76" s="3">
-        <v>35100</v>
+        <v>35600</v>
       </c>
       <c r="K76" s="3">
         <v>33400</v>
@@ -4936,10 +4936,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="E81" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="F81" s="3">
         <v>-1900</v>
@@ -5434,7 +5434,7 @@
         <v>-500</v>
       </c>
       <c r="J89" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="K89" s="3">
         <v>-500</v>
@@ -5701,7 +5701,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="E94" s="3">
         <v>-2600</v>
@@ -5710,7 +5710,7 @@
         <v>-2000</v>
       </c>
       <c r="G94" s="3">
-        <v>-6200</v>
+        <v>-6300</v>
       </c>
       <c r="H94" s="3">
         <v>-2000</v>
@@ -6060,13 +6060,13 @@
         <v>100</v>
       </c>
       <c r="G100" s="3">
-        <v>35100</v>
+        <v>35600</v>
       </c>
       <c r="H100" s="3">
         <v>600</v>
       </c>
       <c r="I100" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -6181,7 +6181,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4900</v>
+        <v>-5000</v>
       </c>
       <c r="E102" s="3">
         <v>-3300</v>
@@ -6190,13 +6190,13 @@
         <v>-2900</v>
       </c>
       <c r="G102" s="3">
-        <v>28100</v>
+        <v>28500</v>
       </c>
       <c r="H102" s="3">
-        <v>-2100</v>
+        <v>-2200</v>
       </c>
       <c r="I102" s="3">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="J102" s="3">
         <v>-800</v>

--- a/AAII_Financials/Quarterly/BNNLF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNNLF_QTR_FIN.xlsx
@@ -2646,16 +2646,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>21500</v>
+        <v>21600</v>
       </c>
       <c r="E42" s="3">
-        <v>27300</v>
+        <v>27400</v>
       </c>
       <c r="F42" s="3">
-        <v>30700</v>
+        <v>30900</v>
       </c>
       <c r="G42" s="3">
-        <v>29900</v>
+        <v>30100</v>
       </c>
       <c r="H42" s="3">
         <v>5600</v>
@@ -2906,22 +2906,22 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>24000</v>
+        <v>24200</v>
       </c>
       <c r="E46" s="3">
-        <v>28900</v>
+        <v>29100</v>
       </c>
       <c r="F46" s="3">
-        <v>32000</v>
+        <v>32200</v>
       </c>
       <c r="G46" s="3">
-        <v>39600</v>
+        <v>39800</v>
       </c>
       <c r="H46" s="3">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="I46" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="J46" s="3">
         <v>2100</v>
@@ -2974,7 +2974,7 @@
         <v>3200</v>
       </c>
       <c r="E47" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="F47" s="3">
         <v>6000</v>
@@ -3036,25 +3036,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>44500</v>
+        <v>44800</v>
       </c>
       <c r="E48" s="3">
+        <v>40500</v>
+      </c>
+      <c r="F48" s="3">
         <v>40200</v>
       </c>
-      <c r="F48" s="3">
-        <v>40000</v>
-      </c>
       <c r="G48" s="3">
-        <v>40300</v>
+        <v>40500</v>
       </c>
       <c r="H48" s="3">
-        <v>37200</v>
+        <v>37400</v>
       </c>
       <c r="I48" s="3">
-        <v>36300</v>
+        <v>36500</v>
       </c>
       <c r="J48" s="3">
-        <v>33900</v>
+        <v>34100</v>
       </c>
       <c r="K48" s="3">
         <v>31100</v>
@@ -3426,25 +3426,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>71700</v>
+        <v>72200</v>
       </c>
       <c r="E54" s="3">
-        <v>75300</v>
+        <v>75700</v>
       </c>
       <c r="F54" s="3">
-        <v>77900</v>
+        <v>78400</v>
       </c>
       <c r="G54" s="3">
-        <v>79900</v>
+        <v>80300</v>
       </c>
       <c r="H54" s="3">
-        <v>43400</v>
+        <v>43700</v>
       </c>
       <c r="I54" s="3">
-        <v>44600</v>
+        <v>44900</v>
       </c>
       <c r="J54" s="3">
-        <v>36000</v>
+        <v>36200</v>
       </c>
       <c r="K54" s="3">
         <v>33800</v>
@@ -3754,7 +3754,7 @@
         <v>200</v>
       </c>
       <c r="J60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K60" s="3">
         <v>200</v>
@@ -4129,7 +4129,7 @@
         <v>800</v>
       </c>
       <c r="E66" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F66" s="3">
         <v>900</v>
@@ -4476,25 +4476,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-44100</v>
+        <v>-44400</v>
       </c>
       <c r="E72" s="3">
-        <v>-40800</v>
+        <v>-41000</v>
       </c>
       <c r="F72" s="3">
-        <v>-40100</v>
+        <v>-40400</v>
       </c>
       <c r="G72" s="3">
-        <v>-38700</v>
+        <v>-38900</v>
       </c>
       <c r="H72" s="3">
-        <v>-37900</v>
+        <v>-38100</v>
       </c>
       <c r="I72" s="3">
-        <v>-37100</v>
+        <v>-37300</v>
       </c>
       <c r="J72" s="3">
-        <v>-36600</v>
+        <v>-36800</v>
       </c>
       <c r="K72" s="3">
         <v>-35100</v>
@@ -4736,25 +4736,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>70900</v>
+        <v>71400</v>
       </c>
       <c r="E76" s="3">
-        <v>74000</v>
+        <v>74500</v>
       </c>
       <c r="F76" s="3">
-        <v>77000</v>
+        <v>77500</v>
       </c>
       <c r="G76" s="3">
-        <v>78600</v>
+        <v>79100</v>
       </c>
       <c r="H76" s="3">
-        <v>42800</v>
+        <v>43100</v>
       </c>
       <c r="I76" s="3">
-        <v>44200</v>
+        <v>44500</v>
       </c>
       <c r="J76" s="3">
-        <v>35600</v>
+        <v>35800</v>
       </c>
       <c r="K76" s="3">
         <v>33400</v>
@@ -5707,10 +5707,10 @@
         <v>-2600</v>
       </c>
       <c r="F94" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="G94" s="3">
-        <v>-6300</v>
+        <v>-6400</v>
       </c>
       <c r="H94" s="3">
         <v>-2000</v>
@@ -6060,7 +6060,7 @@
         <v>100</v>
       </c>
       <c r="G100" s="3">
-        <v>35600</v>
+        <v>35800</v>
       </c>
       <c r="H100" s="3">
         <v>600</v>
@@ -6190,7 +6190,7 @@
         <v>-2900</v>
       </c>
       <c r="G102" s="3">
-        <v>28500</v>
+        <v>28600</v>
       </c>
       <c r="H102" s="3">
         <v>-2200</v>
